--- a/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_BCB.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_BCB.xlsx
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Anjo | A. Rocha Gomes | E. Dias | J. Luz | J. Malheiro (14.4 min)</t>
+          <t>A. Anjo | A. Gomes | E. Dias | J. Luz | J. Malheiro (14.4 min)</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Anjo | A. Rocha Gomes | E. Dias | J. Luz | J. Malheiro (8.3 net)</t>
+          <t>A. Anjo | A. Gomes | E. Dias | J. Luz | J. Malheiro (8.3 net)</t>
         </is>
       </c>
     </row>
@@ -1323,13 +1323,13 @@
         <v>77.59999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3">
@@ -1342,13 +1342,13 @@
         <v>90.7</v>
       </c>
       <c r="C3" t="n">
-        <v>97.8</v>
+        <v>97.3</v>
       </c>
       <c r="D3" t="n">
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.1</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="4">
@@ -1361,13 +1361,13 @@
         <v>96.90000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>97.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="5">
@@ -1380,13 +1380,13 @@
         <v>-6.1</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.1</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="6">
@@ -1399,7 +1399,7 @@
         <v>12.3</v>
       </c>
       <c r="C6" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
@@ -1456,13 +1456,13 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="10">
@@ -1478,7 +1478,7 @@
         <v>0.4</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with A. Anjo, P. Oliveira, and A. Rocha Gomes; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with A. Anjo, P. Oliveira, and A. Gomes; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -2106,8 +2106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
+          <t>BCB_A._GOMES</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
+          <t>BCB_A._GOMES</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BCB_A._ROCHA_GOMES</t>
+          <t>BCB_A._GOMES</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Rocha Gomes</t>
+          <t>A. Gomes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
